--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.6946128758611</v>
+        <v>5.63787459232743</v>
       </c>
       <c r="D2" t="n">
-        <v>34.58380665559654</v>
+        <v>5.619868581534438</v>
       </c>
       <c r="E2" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F2" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.54182407242668</v>
+        <v>3.988046411769335</v>
       </c>
       <c r="D3" t="n">
-        <v>24.34563723215087</v>
+        <v>3.956166050224516</v>
       </c>
       <c r="E3" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F3" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.30490840401725</v>
+        <v>6.224547615652803</v>
       </c>
       <c r="D4" t="n">
-        <v>37.79217485473056</v>
+        <v>6.141228413893717</v>
       </c>
       <c r="E4" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F4" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.672704366241</v>
+        <v>2.059314459514163</v>
       </c>
       <c r="D5" t="n">
-        <v>12.09816052836852</v>
+        <v>1.965951085859885</v>
       </c>
       <c r="E5" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F5" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.36093351536356</v>
+        <v>4.446151696246578</v>
       </c>
       <c r="D6" t="n">
-        <v>27.9331820880708</v>
+        <v>4.539142089311505</v>
       </c>
       <c r="E6" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F6" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.10742029174017</v>
+        <v>3.917455797407778</v>
       </c>
       <c r="D7" t="n">
-        <v>24.14048493359516</v>
+        <v>3.922828801709213</v>
       </c>
       <c r="E7" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F7" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.54864039960233</v>
+        <v>2.201654064935378</v>
       </c>
       <c r="D8" t="n">
-        <v>14.4998765426843</v>
+        <v>2.356229938186199</v>
       </c>
       <c r="E8" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F8" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.43665168800661</v>
+        <v>4.295955899301074</v>
       </c>
       <c r="D9" t="n">
-        <v>6.171419589777249</v>
+        <v>1.002855683338803</v>
       </c>
       <c r="E9" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F9" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>10.58218233531429</v>
+        <v>1.719604629488573</v>
       </c>
       <c r="D10" t="n">
-        <v>10.56301609451545</v>
+        <v>1.71649011535876</v>
       </c>
       <c r="E10" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F10" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.53293847671923</v>
+        <v>4.474102502466875</v>
       </c>
       <c r="D11" t="n">
-        <v>22.85711116620378</v>
+        <v>3.714280564508115</v>
       </c>
       <c r="E11" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F11" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.7410316960164</v>
+        <v>4.507917650602665</v>
       </c>
       <c r="D12" t="n">
-        <v>27.70795887789941</v>
+        <v>4.502543317658654</v>
       </c>
       <c r="E12" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F12" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.67253931817178</v>
+        <v>5.634287639202914</v>
       </c>
       <c r="D13" t="n">
-        <v>19.05618411974093</v>
+        <v>3.096629919457902</v>
       </c>
       <c r="E13" t="n">
-        <v>8.552314818166643</v>
+        <v>1.38975115795208</v>
       </c>
       <c r="F13" t="n">
-        <v>9.265695657562476</v>
+        <v>1.505675544353902</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
